--- a/backend/data/audit_report_templates/financial_statements/soe_standalone.xlsx
+++ b/backend/data/audit_report_templates/financial_statements/soe_standalone.xlsx
@@ -2296,7 +2296,7 @@
       <c r="C3" s="148" t="n"/>
       <c r="D3" s="149" t="inlineStr">
         <is>
-          <t>金额单位：元</t>
+          <t>金额单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,11 @@
           <t xml:space="preserve">  货币资金</t>
         </is>
       </c>
-      <c r="B6" s="154" t="n"/>
+      <c r="B6" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-002}}</t>
+        </is>
+      </c>
       <c r="C6" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-002:current}}</t>
@@ -2392,7 +2396,11 @@
           <t xml:space="preserve">  交易性金融资产</t>
         </is>
       </c>
-      <c r="B9" s="154" t="n"/>
+      <c r="B9" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-005}}</t>
+        </is>
+      </c>
       <c r="C9" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-005:current}}</t>
@@ -2410,7 +2418,11 @@
           <t xml:space="preserve">  衍生金融资产</t>
         </is>
       </c>
-      <c r="B10" s="154" t="n"/>
+      <c r="B10" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-006}}</t>
+        </is>
+      </c>
       <c r="C10" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-006:current}}</t>
@@ -2428,7 +2440,11 @@
           <t xml:space="preserve">  应收票据</t>
         </is>
       </c>
-      <c r="B11" s="154" t="n"/>
+      <c r="B11" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-007}}</t>
+        </is>
+      </c>
       <c r="C11" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-007:current}}</t>
@@ -2446,7 +2462,11 @@
           <t xml:space="preserve">  应收账款</t>
         </is>
       </c>
-      <c r="B12" s="154" t="n"/>
+      <c r="B12" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-008}}</t>
+        </is>
+      </c>
       <c r="C12" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-008:current}}</t>
@@ -2464,7 +2484,11 @@
           <t xml:space="preserve">  应收款项融资</t>
         </is>
       </c>
-      <c r="B13" s="154" t="n"/>
+      <c r="B13" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-009}}</t>
+        </is>
+      </c>
       <c r="C13" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-009:current}}</t>
@@ -2482,7 +2506,11 @@
           <t xml:space="preserve">  预付款项</t>
         </is>
       </c>
-      <c r="B14" s="154" t="n"/>
+      <c r="B14" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-010}}</t>
+        </is>
+      </c>
       <c r="C14" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-010:current}}</t>
@@ -2554,7 +2582,11 @@
           <t xml:space="preserve">  应收资金集中管理款</t>
         </is>
       </c>
-      <c r="B18" s="154" t="n"/>
+      <c r="B18" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-014}}</t>
+        </is>
+      </c>
       <c r="C18" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-014:current}}</t>
@@ -2577,7 +2609,11 @@
           <t xml:space="preserve">  其他应收款</t>
         </is>
       </c>
-      <c r="B19" s="154" t="n"/>
+      <c r="B19" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-015}}</t>
+        </is>
+      </c>
       <c r="C19" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-015:current}}</t>
@@ -2631,7 +2667,11 @@
           <t xml:space="preserve">  存货</t>
         </is>
       </c>
-      <c r="B22" s="154" t="n"/>
+      <c r="B22" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-018}}</t>
+        </is>
+      </c>
       <c r="C22" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-018:current}}</t>
@@ -2690,7 +2730,11 @@
           <t xml:space="preserve">  合同资产</t>
         </is>
       </c>
-      <c r="B25" s="154" t="n"/>
+      <c r="B25" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-021}}</t>
+        </is>
+      </c>
       <c r="C25" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-021:current}}</t>
@@ -2744,7 +2788,11 @@
           <t xml:space="preserve">  持有待售资产</t>
         </is>
       </c>
-      <c r="B28" s="154" t="n"/>
+      <c r="B28" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-024}}</t>
+        </is>
+      </c>
       <c r="C28" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-024:current}}</t>
@@ -2762,7 +2810,11 @@
           <t xml:space="preserve">  一年内到期的非流动资产</t>
         </is>
       </c>
-      <c r="B29" s="154" t="n"/>
+      <c r="B29" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-025}}</t>
+        </is>
+      </c>
       <c r="C29" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-025:current}}</t>
@@ -2780,7 +2832,11 @@
           <t xml:space="preserve">  其他流动资产</t>
         </is>
       </c>
-      <c r="B30" s="154" t="n"/>
+      <c r="B30" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-026}}</t>
+        </is>
+      </c>
       <c r="C30" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-026:current}}</t>
@@ -2847,7 +2903,11 @@
           <t xml:space="preserve">  债权投资</t>
         </is>
       </c>
-      <c r="B34" s="154" t="n"/>
+      <c r="B34" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-030}}</t>
+        </is>
+      </c>
       <c r="C34" s="172" t="inlineStr">
         <is>
           <t>{{row:BS-030:current}}</t>
@@ -2865,7 +2925,11 @@
           <t xml:space="preserve">  其他债权投资</t>
         </is>
       </c>
-      <c r="B35" s="154" t="n"/>
+      <c r="B35" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-031}}</t>
+        </is>
+      </c>
       <c r="C35" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-031:current}}</t>
@@ -2883,7 +2947,11 @@
           <t xml:space="preserve">  长期应收款</t>
         </is>
       </c>
-      <c r="B36" s="154" t="n"/>
+      <c r="B36" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-032}}</t>
+        </is>
+      </c>
       <c r="C36" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-032:current}}</t>
@@ -2901,7 +2969,11 @@
           <t xml:space="preserve">  长期股权投资</t>
         </is>
       </c>
-      <c r="B37" s="154" t="n"/>
+      <c r="B37" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-033}}</t>
+        </is>
+      </c>
       <c r="C37" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-033:current}}</t>
@@ -2919,7 +2991,11 @@
           <t xml:space="preserve">  其他权益工具投资</t>
         </is>
       </c>
-      <c r="B38" s="154" t="n"/>
+      <c r="B38" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-034}}</t>
+        </is>
+      </c>
       <c r="C38" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-034:current}}</t>
@@ -2937,7 +3013,11 @@
           <t xml:space="preserve">  其他非流动金融资产</t>
         </is>
       </c>
-      <c r="B39" s="154" t="n"/>
+      <c r="B39" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-035}}</t>
+        </is>
+      </c>
       <c r="C39" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-035:current}}</t>
@@ -2955,7 +3035,11 @@
           <t xml:space="preserve">  投资性房地产</t>
         </is>
       </c>
-      <c r="B40" s="154" t="n"/>
+      <c r="B40" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-036}}</t>
+        </is>
+      </c>
       <c r="C40" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-036:current}}</t>
@@ -2973,7 +3057,11 @@
           <t xml:space="preserve">  固定资产</t>
         </is>
       </c>
-      <c r="B41" s="154" t="n"/>
+      <c r="B41" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-037}}</t>
+        </is>
+      </c>
       <c r="C41" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-037:current}}</t>
@@ -3045,7 +3133,11 @@
           <t xml:space="preserve">  在建工程</t>
         </is>
       </c>
-      <c r="B45" s="154" t="n"/>
+      <c r="B45" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-041}}</t>
+        </is>
+      </c>
       <c r="C45" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-041:current}}</t>
@@ -3063,7 +3155,11 @@
           <t xml:space="preserve">  生产性生物资产</t>
         </is>
       </c>
-      <c r="B46" s="154" t="n"/>
+      <c r="B46" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-042}}</t>
+        </is>
+      </c>
       <c r="C46" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-042:current}}</t>
@@ -3081,7 +3177,11 @@
           <t xml:space="preserve">  油气资产</t>
         </is>
       </c>
-      <c r="B47" s="154" t="n"/>
+      <c r="B47" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-043}}</t>
+        </is>
+      </c>
       <c r="C47" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-043:current}}</t>
@@ -3099,7 +3199,11 @@
           <t xml:space="preserve">  使用权资产</t>
         </is>
       </c>
-      <c r="B48" s="154" t="n"/>
+      <c r="B48" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-044}}</t>
+        </is>
+      </c>
       <c r="C48" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-044:current}}</t>
@@ -3117,7 +3221,11 @@
           <t xml:space="preserve">  无形资产</t>
         </is>
       </c>
-      <c r="B49" s="154" t="n"/>
+      <c r="B49" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-045}}</t>
+        </is>
+      </c>
       <c r="C49" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-045:current}}</t>
@@ -3135,7 +3243,11 @@
           <t xml:space="preserve">  开发支出</t>
         </is>
       </c>
-      <c r="B50" s="154" t="n"/>
+      <c r="B50" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-046}}</t>
+        </is>
+      </c>
       <c r="C50" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-046:current}}</t>
@@ -3153,7 +3265,11 @@
           <t xml:space="preserve">  商誉</t>
         </is>
       </c>
-      <c r="B51" s="154" t="n"/>
+      <c r="B51" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-047}}</t>
+        </is>
+      </c>
       <c r="C51" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-047:current}}</t>
@@ -3171,7 +3287,11 @@
           <t xml:space="preserve">  长期待摊费用</t>
         </is>
       </c>
-      <c r="B52" s="154" t="n"/>
+      <c r="B52" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-048}}</t>
+        </is>
+      </c>
       <c r="C52" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-048:current}}</t>
@@ -3207,7 +3327,11 @@
           <t xml:space="preserve">  其他非流动资产</t>
         </is>
       </c>
-      <c r="B54" s="154" t="n"/>
+      <c r="B54" s="154" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-050}}</t>
+        </is>
+      </c>
       <c r="C54" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-050:current}}</t>
@@ -3530,7 +3654,7 @@
       <c r="C3" s="148" t="n"/>
       <c r="D3" s="149" t="inlineStr">
         <is>
-          <t>金额单位：元</t>
+          <t>金额单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3696,11 @@
           <t xml:space="preserve">  短期借款</t>
         </is>
       </c>
-      <c r="B6" s="152" t="n"/>
+      <c r="B6" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-055}}</t>
+        </is>
+      </c>
       <c r="C6" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-055:current}}</t>
@@ -3626,7 +3754,11 @@
           <t xml:space="preserve">  交易性金融负债</t>
         </is>
       </c>
-      <c r="B9" s="152" t="n"/>
+      <c r="B9" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-058}}</t>
+        </is>
+      </c>
       <c r="C9" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-058:current}}</t>
@@ -3644,7 +3776,11 @@
           <t xml:space="preserve">  衍生金融负债</t>
         </is>
       </c>
-      <c r="B10" s="152" t="n"/>
+      <c r="B10" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-059}}</t>
+        </is>
+      </c>
       <c r="C10" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-059:current}}</t>
@@ -3662,7 +3798,11 @@
           <t xml:space="preserve">  应付票据</t>
         </is>
       </c>
-      <c r="B11" s="152" t="n"/>
+      <c r="B11" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-060}}</t>
+        </is>
+      </c>
       <c r="C11" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-060:current}}</t>
@@ -3680,7 +3820,11 @@
           <t xml:space="preserve">  应付账款</t>
         </is>
       </c>
-      <c r="B12" s="152" t="n"/>
+      <c r="B12" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-061}}</t>
+        </is>
+      </c>
       <c r="C12" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-061:current}}</t>
@@ -3698,7 +3842,11 @@
           <t xml:space="preserve">  预收款项</t>
         </is>
       </c>
-      <c r="B13" s="152" t="n"/>
+      <c r="B13" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-062}}</t>
+        </is>
+      </c>
       <c r="C13" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-062:current}}</t>
@@ -3716,7 +3864,11 @@
           <t xml:space="preserve">  合同负债</t>
         </is>
       </c>
-      <c r="B14" s="152" t="n"/>
+      <c r="B14" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-063}}</t>
+        </is>
+      </c>
       <c r="C14" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-063:current}}</t>
@@ -3824,7 +3976,11 @@
           <t xml:space="preserve">  应付职工薪酬</t>
         </is>
       </c>
-      <c r="B20" s="152" t="n"/>
+      <c r="B20" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-069}}</t>
+        </is>
+      </c>
       <c r="C20" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-069:current}}</t>
@@ -3896,7 +4052,11 @@
           <t xml:space="preserve">  应交税费</t>
         </is>
       </c>
-      <c r="B24" s="152" t="n"/>
+      <c r="B24" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-073}}</t>
+        </is>
+      </c>
       <c r="C24" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-073:current}}</t>
@@ -3932,7 +4092,11 @@
           <t xml:space="preserve">  其他应付款</t>
         </is>
       </c>
-      <c r="B26" s="152" t="n"/>
+      <c r="B26" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-075}}</t>
+        </is>
+      </c>
       <c r="C26" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-075:current}}</t>
@@ -4004,7 +4168,11 @@
           <t xml:space="preserve">  持有待售负债</t>
         </is>
       </c>
-      <c r="B30" s="152" t="n"/>
+      <c r="B30" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-079}}</t>
+        </is>
+      </c>
       <c r="C30" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-079:current}}</t>
@@ -4022,7 +4190,11 @@
           <t xml:space="preserve">  一年内到期的非流动负债</t>
         </is>
       </c>
-      <c r="B31" s="152" t="n"/>
+      <c r="B31" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-080}}</t>
+        </is>
+      </c>
       <c r="C31" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-080:current}}</t>
@@ -4040,7 +4212,11 @@
           <t xml:space="preserve">  其他流动负债</t>
         </is>
       </c>
-      <c r="B32" s="152" t="n"/>
+      <c r="B32" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-081}}</t>
+        </is>
+      </c>
       <c r="C32" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-081:current}}</t>
@@ -4107,7 +4283,11 @@
           <t xml:space="preserve">  长期借款</t>
         </is>
       </c>
-      <c r="B36" s="152" t="n"/>
+      <c r="B36" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-085}}</t>
+        </is>
+      </c>
       <c r="C36" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-085:current}}</t>
@@ -4125,7 +4305,11 @@
           <t xml:space="preserve">  应付债券</t>
         </is>
       </c>
-      <c r="B37" s="152" t="n"/>
+      <c r="B37" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-086}}</t>
+        </is>
+      </c>
       <c r="C37" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-086:current}}</t>
@@ -4215,7 +4399,11 @@
           <t xml:space="preserve">  租赁负债</t>
         </is>
       </c>
-      <c r="B42" s="152" t="n"/>
+      <c r="B42" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-091}}</t>
+        </is>
+      </c>
       <c r="C42" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-091:current}}</t>
@@ -4233,7 +4421,11 @@
           <t xml:space="preserve">  长期应付款</t>
         </is>
       </c>
-      <c r="B43" s="152" t="n"/>
+      <c r="B43" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-092}}</t>
+        </is>
+      </c>
       <c r="C43" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-092:current}}</t>
@@ -4251,7 +4443,11 @@
           <t xml:space="preserve">  长期应付职工薪酬</t>
         </is>
       </c>
-      <c r="B44" s="152" t="n"/>
+      <c r="B44" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-093}}</t>
+        </is>
+      </c>
       <c r="C44" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-093:current}}</t>
@@ -4269,7 +4465,11 @@
           <t xml:space="preserve">  预计负债</t>
         </is>
       </c>
-      <c r="B45" s="152" t="n"/>
+      <c r="B45" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-094}}</t>
+        </is>
+      </c>
       <c r="C45" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-094:current}}</t>
@@ -4292,7 +4492,11 @@
           <t xml:space="preserve">  递延收益</t>
         </is>
       </c>
-      <c r="B46" s="152" t="n"/>
+      <c r="B46" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-095}}</t>
+        </is>
+      </c>
       <c r="C46" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-095:current}}</t>
@@ -4328,7 +4532,11 @@
           <t xml:space="preserve">  其他非流动负债</t>
         </is>
       </c>
-      <c r="B48" s="152" t="n"/>
+      <c r="B48" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-097}}</t>
+        </is>
+      </c>
       <c r="C48" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-097:current}}</t>
@@ -4407,7 +4615,11 @@
           <t xml:space="preserve">  实收资本</t>
         </is>
       </c>
-      <c r="B53" s="152" t="n"/>
+      <c r="B53" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-102}}</t>
+        </is>
+      </c>
       <c r="C53" s="177">
         <f>SUM(C54:C58)</f>
         <v/>
@@ -4564,7 +4776,11 @@
           <t xml:space="preserve">  其他权益工具</t>
         </is>
       </c>
-      <c r="B61" s="152" t="n"/>
+      <c r="B61" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-110}}</t>
+        </is>
+      </c>
       <c r="C61" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-110:current}}</t>
@@ -4618,7 +4834,11 @@
           <t xml:space="preserve">  资本公积</t>
         </is>
       </c>
-      <c r="B64" s="152" t="n"/>
+      <c r="B64" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-113}}</t>
+        </is>
+      </c>
       <c r="C64" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-113:current}}</t>
@@ -4690,7 +4910,11 @@
           <t xml:space="preserve">  专项储备</t>
         </is>
       </c>
-      <c r="B68" s="152" t="n"/>
+      <c r="B68" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-117}}</t>
+        </is>
+      </c>
       <c r="C68" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-117:current}}</t>
@@ -4708,7 +4932,11 @@
           <t xml:space="preserve">  盈余公积</t>
         </is>
       </c>
-      <c r="B69" s="152" t="n"/>
+      <c r="B69" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-118}}</t>
+        </is>
+      </c>
       <c r="C69" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-118:current}}</t>
@@ -4834,7 +5062,11 @@
           <t xml:space="preserve">  未分配利润</t>
         </is>
       </c>
-      <c r="B76" s="152" t="n"/>
+      <c r="B76" s="152" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-125}}</t>
+        </is>
+      </c>
       <c r="C76" s="177" t="inlineStr">
         <is>
           <t>{{row:BS-125:current}}</t>
@@ -5148,7 +5380,7 @@
       </c>
       <c r="D3" s="83" t="inlineStr">
         <is>
-          <t>金额单位：元</t>
+          <t>金额单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5792,11 @@
           <t xml:space="preserve">                    销售费用</t>
         </is>
       </c>
-      <c r="B26" s="125" t="n"/>
+      <c r="B26" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-022}}</t>
+        </is>
+      </c>
       <c r="C26" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-022:current}}</t>
@@ -5578,7 +5814,11 @@
           <t xml:space="preserve">                    管理费用</t>
         </is>
       </c>
-      <c r="B27" s="125" t="n"/>
+      <c r="B27" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-023}}</t>
+        </is>
+      </c>
       <c r="C27" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-023:current}}</t>
@@ -5596,7 +5836,11 @@
           <t xml:space="preserve">                    研发费用</t>
         </is>
       </c>
-      <c r="B28" s="125" t="n"/>
+      <c r="B28" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-024}}</t>
+        </is>
+      </c>
       <c r="C28" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-024:current}}</t>
@@ -5614,7 +5858,11 @@
           <t xml:space="preserve">                    财务费用</t>
         </is>
       </c>
-      <c r="B29" s="125" t="n"/>
+      <c r="B29" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-025}}</t>
+        </is>
+      </c>
       <c r="C29" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-025:current}}</t>
@@ -5799,7 +6047,11 @@
           <t xml:space="preserve">                    净敞口套期收益（损失以“－”号填列）</t>
         </is>
       </c>
-      <c r="B39" s="125" t="n"/>
+      <c r="B39" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-035}}</t>
+        </is>
+      </c>
       <c r="C39" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-035:current}}</t>
@@ -5817,7 +6069,11 @@
           <t xml:space="preserve">                    公允价值变动收益（损失以“－”号填列）</t>
         </is>
       </c>
-      <c r="B40" s="125" t="n"/>
+      <c r="B40" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-036}}</t>
+        </is>
+      </c>
       <c r="C40" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-036:current}}</t>
@@ -5835,7 +6091,11 @@
           <t xml:space="preserve">                    信用减值损失（损失以“－”号填列）</t>
         </is>
       </c>
-      <c r="B41" s="125" t="n"/>
+      <c r="B41" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-037}}</t>
+        </is>
+      </c>
       <c r="C41" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-037:current}}</t>
@@ -5858,7 +6118,11 @@
           <t xml:space="preserve">                    资产减值损失（损失以“－”号填列）</t>
         </is>
       </c>
-      <c r="B42" s="125" t="n"/>
+      <c r="B42" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-038}}</t>
+        </is>
+      </c>
       <c r="C42" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-038:current}}</t>
@@ -5876,7 +6140,11 @@
           <t xml:space="preserve">                    资产处置收益（损失以“－”号填列）</t>
         </is>
       </c>
-      <c r="B43" s="125" t="n"/>
+      <c r="B43" s="125" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-039}}</t>
+        </is>
+      </c>
       <c r="C43" s="187" t="inlineStr">
         <is>
           <t>{{row:IS-039:current}}</t>
@@ -6695,7 +6963,7 @@
       <c r="C3" s="82" t="n"/>
       <c r="D3" s="83" t="inlineStr">
         <is>
-          <t>金额单位：元</t>
+          <t>金额单位：{{currency_unit}}</t>
         </is>
       </c>
       <c r="E3" s="81" t="n"/>
@@ -8049,7 +8317,7 @@
     <row r="3" ht="18" customFormat="1" customHeight="1" s="81">
       <c r="A3" s="82" t="inlineStr">
         <is>
-          <t>编制单位：</t>
+          <t>编制单位：{{company_full_name}}</t>
         </is>
       </c>
       <c r="B3" s="82" t="n"/>
@@ -8059,7 +8327,7 @@
       <c r="F3" s="82" t="n"/>
       <c r="G3" s="82" t="inlineStr">
         <is>
-          <t>2025年度</t>
+          <t>{{audit_year}}年度</t>
         </is>
       </c>
       <c r="H3" s="81" t="n"/>
@@ -8413,32 +8681,104 @@
       <c r="B9" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="203" t="n"/>
-      <c r="D9" s="203" t="n"/>
+      <c r="C9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E9" s="203" t="n"/>
       <c r="F9" s="203" t="n"/>
-      <c r="G9" s="203" t="n"/>
-      <c r="H9" s="203" t="n"/>
-      <c r="I9" s="203" t="n"/>
-      <c r="J9" s="203" t="n"/>
-      <c r="K9" s="203" t="n"/>
-      <c r="L9" s="203" t="n"/>
-      <c r="M9" s="203" t="n"/>
+      <c r="G9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N9" s="203">
         <f>SUM(C9:G9)+SUM(I9:M9)-H9</f>
         <v/>
       </c>
-      <c r="O9" s="204" t="n"/>
-      <c r="P9" s="203" t="n"/>
+      <c r="O9" s="204" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q9" s="203" t="n"/>
       <c r="R9" s="203" t="n"/>
-      <c r="S9" s="203" t="n"/>
-      <c r="T9" s="203" t="n"/>
-      <c r="U9" s="203" t="n"/>
-      <c r="V9" s="203" t="n"/>
-      <c r="W9" s="203" t="n"/>
-      <c r="X9" s="203" t="n"/>
-      <c r="Y9" s="203" t="n"/>
+      <c r="S9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y9" s="203" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z9" s="203">
         <f>SUM(O9:S9)+SUM(U9:Y9)-T9</f>
         <v/>
@@ -8453,32 +8793,104 @@
       <c r="B10" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="205" t="n"/>
-      <c r="D10" s="205" t="n"/>
+      <c r="C10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E10" s="205" t="n"/>
       <c r="F10" s="205" t="n"/>
-      <c r="G10" s="205" t="n"/>
-      <c r="H10" s="205" t="n"/>
-      <c r="I10" s="205" t="n"/>
-      <c r="J10" s="205" t="n"/>
-      <c r="K10" s="205" t="n"/>
-      <c r="L10" s="205" t="n"/>
-      <c r="M10" s="205" t="n"/>
+      <c r="G10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N10" s="205">
         <f>SUM(C10:G10)+SUM(I10:M10)-H10</f>
         <v/>
       </c>
-      <c r="O10" s="206" t="n"/>
-      <c r="P10" s="205" t="n"/>
+      <c r="O10" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q10" s="205" t="n"/>
       <c r="R10" s="205" t="n"/>
-      <c r="S10" s="205" t="n"/>
-      <c r="T10" s="205" t="n"/>
-      <c r="U10" s="205" t="n"/>
-      <c r="V10" s="205" t="n"/>
-      <c r="W10" s="205" t="n"/>
-      <c r="X10" s="205" t="n"/>
-      <c r="Y10" s="205" t="n"/>
+      <c r="S10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y10" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z10" s="205">
         <f>SUM(O10:S10)+SUM(U10:Y10)-T10</f>
         <v/>
@@ -8493,32 +8905,104 @@
       <c r="B11" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="205" t="n"/>
-      <c r="D11" s="205" t="n"/>
+      <c r="C11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E11" s="205" t="n"/>
       <c r="F11" s="205" t="n"/>
-      <c r="G11" s="205" t="n"/>
-      <c r="H11" s="205" t="n"/>
-      <c r="I11" s="205" t="n"/>
-      <c r="J11" s="205" t="n"/>
-      <c r="K11" s="205" t="n"/>
-      <c r="L11" s="205" t="n"/>
-      <c r="M11" s="205" t="n"/>
+      <c r="G11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N11" s="205">
         <f>SUM(C11:G11)+SUM(I11:M11)-H11</f>
         <v/>
       </c>
-      <c r="O11" s="206" t="n"/>
-      <c r="P11" s="205" t="n"/>
+      <c r="O11" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q11" s="205" t="n"/>
       <c r="R11" s="205" t="n"/>
-      <c r="S11" s="205" t="n"/>
-      <c r="T11" s="205" t="n"/>
-      <c r="U11" s="205" t="n"/>
-      <c r="V11" s="205" t="n"/>
-      <c r="W11" s="205" t="n"/>
-      <c r="X11" s="205" t="n"/>
-      <c r="Y11" s="205" t="n"/>
+      <c r="S11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y11" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z11" s="205">
         <f>SUM(O11:S11)+SUM(U11:Y11)-T11</f>
         <v/>
@@ -8533,32 +9017,104 @@
       <c r="B12" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="205" t="n"/>
-      <c r="D12" s="205" t="n"/>
+      <c r="C12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E12" s="205" t="n"/>
       <c r="F12" s="205" t="n"/>
-      <c r="G12" s="205" t="n"/>
-      <c r="H12" s="205" t="n"/>
-      <c r="I12" s="205" t="n"/>
-      <c r="J12" s="205" t="n"/>
-      <c r="K12" s="205" t="n"/>
-      <c r="L12" s="205" t="n"/>
-      <c r="M12" s="205" t="n"/>
+      <c r="G12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N12" s="205">
         <f>SUM(C12:G12)+SUM(I12:M12)-H12</f>
         <v/>
       </c>
-      <c r="O12" s="206" t="n"/>
-      <c r="P12" s="205" t="n"/>
+      <c r="O12" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q12" s="205" t="n"/>
       <c r="R12" s="205" t="n"/>
-      <c r="S12" s="205" t="n"/>
-      <c r="T12" s="205" t="n"/>
-      <c r="U12" s="205" t="n"/>
-      <c r="V12" s="205" t="n"/>
-      <c r="W12" s="205" t="n"/>
-      <c r="X12" s="205" t="n"/>
-      <c r="Y12" s="205" t="n"/>
+      <c r="S12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y12" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z12" s="205">
         <f>SUM(O12:S12)+SUM(U12:Y12)-T12</f>
         <v/>
@@ -8785,32 +9341,104 @@
       <c r="B15" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="205" t="n"/>
-      <c r="D15" s="205" t="n"/>
+      <c r="C15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E15" s="205" t="n"/>
       <c r="F15" s="205" t="n"/>
-      <c r="G15" s="205" t="n"/>
-      <c r="H15" s="205" t="n"/>
-      <c r="I15" s="205" t="n"/>
-      <c r="J15" s="205" t="n"/>
-      <c r="K15" s="205" t="n"/>
-      <c r="L15" s="205" t="n"/>
-      <c r="M15" s="205" t="n"/>
+      <c r="G15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N15" s="205">
         <f>SUM(C15:G15)+SUM(I15:M15)-H15</f>
         <v/>
       </c>
-      <c r="O15" s="206" t="n"/>
-      <c r="P15" s="205" t="n"/>
+      <c r="O15" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q15" s="205" t="n"/>
       <c r="R15" s="205" t="n"/>
-      <c r="S15" s="205" t="n"/>
-      <c r="T15" s="205" t="n"/>
-      <c r="U15" s="205" t="n"/>
-      <c r="V15" s="205" t="n"/>
-      <c r="W15" s="205" t="n"/>
-      <c r="X15" s="205" t="n"/>
-      <c r="Y15" s="205" t="n"/>
+      <c r="S15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y15" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-007:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z15" s="205">
         <f>SUM(O15:S15)+SUM(U15:Y15)-T15</f>
         <v/>
@@ -8931,32 +9559,104 @@
       <c r="B17" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="205" t="n"/>
-      <c r="D17" s="205" t="n"/>
+      <c r="C17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E17" s="205" t="n"/>
       <c r="F17" s="205" t="n"/>
-      <c r="G17" s="205" t="n"/>
-      <c r="H17" s="205" t="n"/>
-      <c r="I17" s="205" t="n"/>
-      <c r="J17" s="205" t="n"/>
-      <c r="K17" s="205" t="n"/>
-      <c r="L17" s="205" t="n"/>
-      <c r="M17" s="205" t="n"/>
+      <c r="G17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N17" s="205">
         <f>SUM(C17:G17)+SUM(I17:M17)-H17</f>
         <v/>
       </c>
-      <c r="O17" s="206" t="n"/>
-      <c r="P17" s="205" t="n"/>
+      <c r="O17" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q17" s="205" t="n"/>
       <c r="R17" s="205" t="n"/>
-      <c r="S17" s="205" t="n"/>
-      <c r="T17" s="205" t="n"/>
-      <c r="U17" s="205" t="n"/>
-      <c r="V17" s="205" t="n"/>
-      <c r="W17" s="205" t="n"/>
-      <c r="X17" s="205" t="n"/>
-      <c r="Y17" s="205" t="n"/>
+      <c r="S17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y17" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-009:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z17" s="205">
         <f>SUM(O17:S17)+SUM(U17:Y17)-T17</f>
         <v/>
@@ -8971,32 +9671,104 @@
       <c r="B18" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="205" t="n"/>
-      <c r="D18" s="205" t="n"/>
+      <c r="C18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E18" s="205" t="n"/>
       <c r="F18" s="205" t="n"/>
-      <c r="G18" s="205" t="n"/>
-      <c r="H18" s="205" t="n"/>
-      <c r="I18" s="205" t="n"/>
-      <c r="J18" s="205" t="n"/>
-      <c r="K18" s="205" t="n"/>
-      <c r="L18" s="205" t="n"/>
-      <c r="M18" s="205" t="n"/>
+      <c r="G18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N18" s="205">
         <f>SUM(C18:G18)+SUM(I18:M18)-H18</f>
         <v/>
       </c>
-      <c r="O18" s="206" t="n"/>
-      <c r="P18" s="205" t="n"/>
+      <c r="O18" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q18" s="205" t="n"/>
       <c r="R18" s="205" t="n"/>
-      <c r="S18" s="205" t="n"/>
-      <c r="T18" s="205" t="n"/>
-      <c r="U18" s="205" t="n"/>
-      <c r="V18" s="205" t="n"/>
-      <c r="W18" s="205" t="n"/>
-      <c r="X18" s="205" t="n"/>
-      <c r="Y18" s="205" t="n"/>
+      <c r="S18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y18" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z18" s="205">
         <f>SUM(O18:S18)+SUM(U18:Y18)-T18</f>
         <v/>
@@ -9011,32 +9783,104 @@
       <c r="B19" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="205" t="n"/>
-      <c r="D19" s="205" t="n"/>
+      <c r="C19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E19" s="205" t="n"/>
       <c r="F19" s="205" t="n"/>
-      <c r="G19" s="205" t="n"/>
-      <c r="H19" s="205" t="n"/>
-      <c r="I19" s="205" t="n"/>
-      <c r="J19" s="205" t="n"/>
-      <c r="K19" s="205" t="n"/>
-      <c r="L19" s="205" t="n"/>
-      <c r="M19" s="205" t="n"/>
+      <c r="G19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N19" s="205">
         <f>SUM(C19:G19)+SUM(I19:M19)-H19</f>
         <v/>
       </c>
-      <c r="O19" s="206" t="n"/>
-      <c r="P19" s="205" t="n"/>
+      <c r="O19" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q19" s="205" t="n"/>
       <c r="R19" s="205" t="n"/>
-      <c r="S19" s="205" t="n"/>
-      <c r="T19" s="205" t="n"/>
-      <c r="U19" s="205" t="n"/>
-      <c r="V19" s="205" t="n"/>
-      <c r="W19" s="205" t="n"/>
-      <c r="X19" s="205" t="n"/>
-      <c r="Y19" s="205" t="n"/>
+      <c r="S19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y19" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z19" s="205">
         <f>SUM(O19:S19)+SUM(U19:Y19)-T19</f>
         <v/>
@@ -9051,32 +9895,104 @@
       <c r="B20" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="207" t="n"/>
-      <c r="D20" s="207" t="n"/>
+      <c r="C20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E20" s="207" t="n"/>
       <c r="F20" s="207" t="n"/>
-      <c r="G20" s="207" t="n"/>
-      <c r="H20" s="207" t="n"/>
-      <c r="I20" s="207" t="n"/>
-      <c r="J20" s="207" t="n"/>
-      <c r="K20" s="207" t="n"/>
-      <c r="L20" s="207" t="n"/>
-      <c r="M20" s="207" t="n"/>
+      <c r="G20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N20" s="205">
         <f>SUM(C20:G20)+SUM(I20:M20)-H20</f>
         <v/>
       </c>
-      <c r="O20" s="208" t="n"/>
-      <c r="P20" s="207" t="n"/>
+      <c r="O20" s="208" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q20" s="207" t="n"/>
       <c r="R20" s="207" t="n"/>
-      <c r="S20" s="207" t="n"/>
-      <c r="T20" s="207" t="n"/>
-      <c r="U20" s="207" t="n"/>
-      <c r="V20" s="207" t="n"/>
-      <c r="W20" s="207" t="n"/>
-      <c r="X20" s="207" t="n"/>
-      <c r="Y20" s="207" t="n"/>
+      <c r="S20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y20" s="207" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z20" s="205">
         <f>SUM(O20:S20)+SUM(U20:Y20)-T20</f>
         <v/>
@@ -9197,32 +10113,104 @@
       <c r="B22" s="57" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="205" t="n"/>
-      <c r="D22" s="205" t="n"/>
+      <c r="C22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E22" s="205" t="n"/>
       <c r="F22" s="205" t="n"/>
-      <c r="G22" s="205" t="n"/>
-      <c r="H22" s="205" t="n"/>
-      <c r="I22" s="205" t="n"/>
-      <c r="J22" s="205" t="n"/>
-      <c r="K22" s="205" t="n"/>
-      <c r="L22" s="205" t="n"/>
-      <c r="M22" s="205" t="n"/>
+      <c r="G22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N22" s="205">
         <f>SUM(C22:G22)+SUM(I22:M22)-H22</f>
         <v/>
       </c>
-      <c r="O22" s="206" t="n"/>
-      <c r="P22" s="205" t="n"/>
+      <c r="O22" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q22" s="205" t="n"/>
       <c r="R22" s="205" t="n"/>
-      <c r="S22" s="205" t="n"/>
-      <c r="T22" s="205" t="n"/>
-      <c r="U22" s="205" t="n"/>
-      <c r="V22" s="205" t="n"/>
-      <c r="W22" s="205" t="n"/>
-      <c r="X22" s="205" t="n"/>
-      <c r="Y22" s="205" t="n"/>
+      <c r="S22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y22" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-014:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z22" s="205">
         <f>SUM(O22:S22)+SUM(U22:Y22)-T22</f>
         <v/>
@@ -9237,32 +10225,104 @@
       <c r="B23" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="205" t="n"/>
-      <c r="D23" s="205" t="n"/>
+      <c r="C23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E23" s="205" t="n"/>
       <c r="F23" s="205" t="n"/>
-      <c r="G23" s="205" t="n"/>
-      <c r="H23" s="205" t="n"/>
-      <c r="I23" s="205" t="n"/>
-      <c r="J23" s="205" t="n"/>
-      <c r="K23" s="205" t="n"/>
-      <c r="L23" s="205" t="n"/>
-      <c r="M23" s="205" t="n"/>
+      <c r="G23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N23" s="205">
         <f>SUM(C23:G23)+SUM(I23:M23)-H23</f>
         <v/>
       </c>
-      <c r="O23" s="206" t="n"/>
-      <c r="P23" s="205" t="n"/>
+      <c r="O23" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q23" s="205" t="n"/>
       <c r="R23" s="205" t="n"/>
-      <c r="S23" s="205" t="n"/>
-      <c r="T23" s="205" t="n"/>
-      <c r="U23" s="205" t="n"/>
-      <c r="V23" s="205" t="n"/>
-      <c r="W23" s="205" t="n"/>
-      <c r="X23" s="205" t="n"/>
-      <c r="Y23" s="205" t="n"/>
+      <c r="S23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y23" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z23" s="205">
         <f>SUM(O23:S23)+SUM(U23:Y23)-T23</f>
         <v/>
@@ -9383,32 +10443,104 @@
       <c r="B25" s="57" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="205" t="n"/>
-      <c r="D25" s="205" t="n"/>
+      <c r="C25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E25" s="205" t="n"/>
       <c r="F25" s="205" t="n"/>
-      <c r="G25" s="205" t="n"/>
-      <c r="H25" s="205" t="n"/>
-      <c r="I25" s="205" t="n"/>
-      <c r="J25" s="205" t="n"/>
-      <c r="K25" s="205" t="n"/>
-      <c r="L25" s="205" t="n"/>
-      <c r="M25" s="205" t="n"/>
+      <c r="G25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N25" s="205">
         <f>SUM(C25:G25)+SUM(I25:M25)-H25</f>
         <v/>
       </c>
-      <c r="O25" s="206" t="n"/>
-      <c r="P25" s="205" t="n"/>
+      <c r="O25" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q25" s="205" t="n"/>
       <c r="R25" s="205" t="n"/>
-      <c r="S25" s="205" t="n"/>
-      <c r="T25" s="205" t="n"/>
-      <c r="U25" s="205" t="n"/>
-      <c r="V25" s="205" t="n"/>
-      <c r="W25" s="205" t="n"/>
-      <c r="X25" s="205" t="n"/>
-      <c r="Y25" s="205" t="n"/>
+      <c r="S25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y25" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z25" s="205">
         <f>SUM(O25:S25)+SUM(U25:Y25)-T25</f>
         <v/>
@@ -9423,32 +10555,104 @@
       <c r="B26" s="57" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="205" t="n"/>
-      <c r="D26" s="205" t="n"/>
+      <c r="C26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E26" s="205" t="n"/>
       <c r="F26" s="205" t="n"/>
-      <c r="G26" s="205" t="n"/>
-      <c r="H26" s="205" t="n"/>
-      <c r="I26" s="205" t="n"/>
-      <c r="J26" s="205" t="n"/>
-      <c r="K26" s="205" t="n"/>
-      <c r="L26" s="205" t="n"/>
-      <c r="M26" s="205" t="n"/>
+      <c r="G26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N26" s="205">
         <f>SUM(C26:G26)+SUM(I26:M26)-H26</f>
         <v/>
       </c>
-      <c r="O26" s="206" t="n"/>
-      <c r="P26" s="205" t="n"/>
+      <c r="O26" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q26" s="205" t="n"/>
       <c r="R26" s="205" t="n"/>
-      <c r="S26" s="205" t="n"/>
-      <c r="T26" s="205" t="n"/>
-      <c r="U26" s="205" t="n"/>
-      <c r="V26" s="205" t="n"/>
-      <c r="W26" s="205" t="n"/>
-      <c r="X26" s="205" t="n"/>
-      <c r="Y26" s="205" t="n"/>
+      <c r="S26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y26" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-018:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z26" s="205">
         <f>SUM(O26:S26)+SUM(U26:Y26)-T26</f>
         <v/>
@@ -9463,32 +10667,104 @@
       <c r="B27" s="57" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="205" t="n"/>
-      <c r="D27" s="205" t="n"/>
+      <c r="C27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E27" s="205" t="n"/>
       <c r="F27" s="205" t="n"/>
-      <c r="G27" s="205" t="n"/>
-      <c r="H27" s="205" t="n"/>
-      <c r="I27" s="205" t="n"/>
-      <c r="J27" s="205" t="n"/>
-      <c r="K27" s="205" t="n"/>
-      <c r="L27" s="205" t="n"/>
-      <c r="M27" s="205" t="n"/>
+      <c r="G27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N27" s="205">
         <f>SUM(C27:G27)+SUM(I27:M27)-H27</f>
         <v/>
       </c>
-      <c r="O27" s="206" t="n"/>
-      <c r="P27" s="205" t="n"/>
+      <c r="O27" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q27" s="205" t="n"/>
       <c r="R27" s="205" t="n"/>
-      <c r="S27" s="205" t="n"/>
-      <c r="T27" s="205" t="n"/>
-      <c r="U27" s="205" t="n"/>
-      <c r="V27" s="205" t="n"/>
-      <c r="W27" s="205" t="n"/>
-      <c r="X27" s="205" t="n"/>
-      <c r="Y27" s="205" t="n"/>
+      <c r="S27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y27" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-019:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z27" s="205">
         <f>SUM(O27:S27)+SUM(U27:Y27)-T27</f>
         <v/>
@@ -9503,32 +10779,104 @@
       <c r="B28" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="205" t="n"/>
-      <c r="D28" s="205" t="n"/>
+      <c r="C28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E28" s="205" t="n"/>
       <c r="F28" s="205" t="n"/>
-      <c r="G28" s="205" t="n"/>
-      <c r="H28" s="205" t="n"/>
-      <c r="I28" s="205" t="n"/>
-      <c r="J28" s="205" t="n"/>
-      <c r="K28" s="205" t="n"/>
-      <c r="L28" s="205" t="n"/>
-      <c r="M28" s="205" t="n"/>
+      <c r="G28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N28" s="205">
         <f>SUM(C28:G28)+SUM(I28:M28)-H28</f>
         <v/>
       </c>
-      <c r="O28" s="206" t="n"/>
-      <c r="P28" s="205" t="n"/>
+      <c r="O28" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q28" s="205" t="n"/>
       <c r="R28" s="205" t="n"/>
-      <c r="S28" s="205" t="n"/>
-      <c r="T28" s="205" t="n"/>
-      <c r="U28" s="205" t="n"/>
-      <c r="V28" s="205" t="n"/>
-      <c r="W28" s="205" t="n"/>
-      <c r="X28" s="205" t="n"/>
-      <c r="Y28" s="205" t="n"/>
+      <c r="S28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y28" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z28" s="205">
         <f>SUM(O28:S28)+SUM(U28:Y28)-T28</f>
         <v/>
@@ -9543,32 +10891,104 @@
       <c r="B29" s="57" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="205" t="n"/>
-      <c r="D29" s="205" t="n"/>
+      <c r="C29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E29" s="205" t="n"/>
       <c r="F29" s="205" t="n"/>
-      <c r="G29" s="205" t="n"/>
-      <c r="H29" s="205" t="n"/>
-      <c r="I29" s="205" t="n"/>
-      <c r="J29" s="205" t="n"/>
-      <c r="K29" s="205" t="n"/>
-      <c r="L29" s="205" t="n"/>
-      <c r="M29" s="205" t="n"/>
+      <c r="G29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N29" s="205">
         <f>SUM(C29:G29)+SUM(I29:M29)-H29</f>
         <v/>
       </c>
-      <c r="O29" s="206" t="n"/>
-      <c r="P29" s="205" t="n"/>
+      <c r="O29" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q29" s="205" t="n"/>
       <c r="R29" s="205" t="n"/>
-      <c r="S29" s="205" t="n"/>
-      <c r="T29" s="205" t="n"/>
-      <c r="U29" s="205" t="n"/>
-      <c r="V29" s="205" t="n"/>
-      <c r="W29" s="205" t="n"/>
-      <c r="X29" s="205" t="n"/>
-      <c r="Y29" s="205" t="n"/>
+      <c r="S29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y29" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z29" s="205">
         <f>SUM(O29:S29)+SUM(U29:Y29)-T29</f>
         <v/>
@@ -9583,32 +11003,104 @@
       <c r="B30" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="205" t="n"/>
-      <c r="D30" s="205" t="n"/>
+      <c r="C30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E30" s="205" t="n"/>
       <c r="F30" s="205" t="n"/>
-      <c r="G30" s="205" t="n"/>
-      <c r="H30" s="205" t="n"/>
-      <c r="I30" s="205" t="n"/>
-      <c r="J30" s="205" t="n"/>
-      <c r="K30" s="205" t="n"/>
-      <c r="L30" s="205" t="n"/>
-      <c r="M30" s="205" t="n"/>
+      <c r="G30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N30" s="205">
         <f>SUM(C30:G30)+SUM(I30:M30)-H30</f>
         <v/>
       </c>
-      <c r="O30" s="206" t="n"/>
-      <c r="P30" s="205" t="n"/>
+      <c r="O30" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q30" s="205" t="n"/>
       <c r="R30" s="205" t="n"/>
-      <c r="S30" s="205" t="n"/>
-      <c r="T30" s="205" t="n"/>
-      <c r="U30" s="205" t="n"/>
-      <c r="V30" s="205" t="n"/>
-      <c r="W30" s="205" t="n"/>
-      <c r="X30" s="205" t="n"/>
-      <c r="Y30" s="205" t="n"/>
+      <c r="S30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y30" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z30" s="205">
         <f>SUM(O30:S30)+SUM(U30:Y30)-T30</f>
         <v/>
@@ -9623,32 +11115,104 @@
       <c r="B31" s="57" t="n">
         <v>23</v>
       </c>
-      <c r="C31" s="205" t="n"/>
-      <c r="D31" s="205" t="n"/>
+      <c r="C31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E31" s="205" t="n"/>
       <c r="F31" s="205" t="n"/>
-      <c r="G31" s="205" t="n"/>
-      <c r="H31" s="205" t="n"/>
-      <c r="I31" s="205" t="n"/>
-      <c r="J31" s="205" t="n"/>
-      <c r="K31" s="205" t="n"/>
-      <c r="L31" s="205" t="n"/>
-      <c r="M31" s="205" t="n"/>
+      <c r="G31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N31" s="205">
         <f>SUM(C31:G31)+SUM(I31:M31)-H31</f>
         <v/>
       </c>
-      <c r="O31" s="206" t="n"/>
-      <c r="P31" s="205" t="n"/>
+      <c r="O31" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q31" s="205" t="n"/>
       <c r="R31" s="205" t="n"/>
-      <c r="S31" s="205" t="n"/>
-      <c r="T31" s="205" t="n"/>
-      <c r="U31" s="205" t="n"/>
-      <c r="V31" s="205" t="n"/>
-      <c r="W31" s="205" t="n"/>
-      <c r="X31" s="205" t="n"/>
-      <c r="Y31" s="205" t="n"/>
+      <c r="S31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y31" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z31" s="205">
         <f>SUM(O31:S31)+SUM(U31:Y31)-T31</f>
         <v/>
@@ -9663,32 +11227,104 @@
       <c r="B32" s="57" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="205" t="n"/>
-      <c r="D32" s="205" t="n"/>
+      <c r="C32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E32" s="205" t="n"/>
       <c r="F32" s="205" t="n"/>
-      <c r="G32" s="205" t="n"/>
-      <c r="H32" s="205" t="n"/>
-      <c r="I32" s="205" t="n"/>
-      <c r="J32" s="205" t="n"/>
-      <c r="K32" s="205" t="n"/>
-      <c r="L32" s="205" t="n"/>
-      <c r="M32" s="205" t="n"/>
+      <c r="G32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N32" s="205">
         <f>SUM(C32:G32)+SUM(I32:M32)-H32</f>
         <v/>
       </c>
-      <c r="O32" s="206" t="n"/>
-      <c r="P32" s="205" t="n"/>
+      <c r="O32" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q32" s="205" t="n"/>
       <c r="R32" s="205" t="n"/>
-      <c r="S32" s="205" t="n"/>
-      <c r="T32" s="205" t="n"/>
-      <c r="U32" s="205" t="n"/>
-      <c r="V32" s="205" t="n"/>
-      <c r="W32" s="205" t="n"/>
-      <c r="X32" s="205" t="n"/>
-      <c r="Y32" s="205" t="n"/>
+      <c r="S32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y32" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z32" s="205">
         <f>SUM(O32:S32)+SUM(U32:Y32)-T32</f>
         <v/>
@@ -9703,32 +11339,104 @@
       <c r="B33" s="57" t="n">
         <v>25</v>
       </c>
-      <c r="C33" s="205" t="n"/>
-      <c r="D33" s="205" t="n"/>
+      <c r="C33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E33" s="205" t="n"/>
       <c r="F33" s="205" t="n"/>
-      <c r="G33" s="205" t="n"/>
-      <c r="H33" s="205" t="n"/>
-      <c r="I33" s="205" t="n"/>
-      <c r="J33" s="205" t="n"/>
-      <c r="K33" s="205" t="n"/>
-      <c r="L33" s="205" t="n"/>
-      <c r="M33" s="205" t="n"/>
+      <c r="G33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N33" s="205">
         <f>SUM(C33:G33)+SUM(I33:M33)-H33</f>
         <v/>
       </c>
-      <c r="O33" s="206" t="n"/>
-      <c r="P33" s="205" t="n"/>
+      <c r="O33" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q33" s="205" t="n"/>
       <c r="R33" s="205" t="n"/>
-      <c r="S33" s="205" t="n"/>
-      <c r="T33" s="205" t="n"/>
-      <c r="U33" s="205" t="n"/>
-      <c r="V33" s="205" t="n"/>
-      <c r="W33" s="205" t="n"/>
-      <c r="X33" s="205" t="n"/>
-      <c r="Y33" s="205" t="n"/>
+      <c r="S33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y33" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z33" s="205">
         <f>SUM(O33:S33)+SUM(U33:Y33)-T33</f>
         <v/>
@@ -9849,32 +11557,104 @@
       <c r="B35" s="57" t="n">
         <v>27</v>
       </c>
-      <c r="C35" s="205" t="n"/>
-      <c r="D35" s="205" t="n"/>
+      <c r="C35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E35" s="205" t="n"/>
       <c r="F35" s="205" t="n"/>
-      <c r="G35" s="205" t="n"/>
-      <c r="H35" s="205" t="n"/>
-      <c r="I35" s="205" t="n"/>
-      <c r="J35" s="205" t="n"/>
-      <c r="K35" s="205" t="n"/>
-      <c r="L35" s="205" t="n"/>
-      <c r="M35" s="205" t="n"/>
+      <c r="G35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N35" s="205">
         <f>SUM(C35:G35)+SUM(I35:M35)-H35</f>
         <v/>
       </c>
-      <c r="O35" s="206" t="n"/>
-      <c r="P35" s="205" t="n"/>
+      <c r="O35" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q35" s="205" t="n"/>
       <c r="R35" s="205" t="n"/>
-      <c r="S35" s="205" t="n"/>
-      <c r="T35" s="205" t="n"/>
-      <c r="U35" s="205" t="n"/>
-      <c r="V35" s="205" t="n"/>
-      <c r="W35" s="205" t="n"/>
-      <c r="X35" s="205" t="n"/>
-      <c r="Y35" s="205" t="n"/>
+      <c r="S35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y35" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z35" s="205">
         <f>SUM(O35:S35)+SUM(U35:Y35)-T35</f>
         <v/>
@@ -9889,32 +11669,104 @@
       <c r="B36" s="57" t="n">
         <v>28</v>
       </c>
-      <c r="C36" s="205" t="n"/>
-      <c r="D36" s="205" t="n"/>
+      <c r="C36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E36" s="205" t="n"/>
       <c r="F36" s="205" t="n"/>
-      <c r="G36" s="205" t="n"/>
-      <c r="H36" s="205" t="n"/>
-      <c r="I36" s="205" t="n"/>
-      <c r="J36" s="205" t="n"/>
-      <c r="K36" s="205" t="n"/>
-      <c r="L36" s="205" t="n"/>
-      <c r="M36" s="205" t="n"/>
+      <c r="G36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N36" s="205">
         <f>SUM(C36:G36)+SUM(I36:M36)-H36</f>
         <v/>
       </c>
-      <c r="O36" s="206" t="n"/>
-      <c r="P36" s="205" t="n"/>
+      <c r="O36" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q36" s="205" t="n"/>
       <c r="R36" s="205" t="n"/>
-      <c r="S36" s="205" t="n"/>
-      <c r="T36" s="205" t="n"/>
-      <c r="U36" s="205" t="n"/>
-      <c r="V36" s="205" t="n"/>
-      <c r="W36" s="205" t="n"/>
-      <c r="X36" s="205" t="n"/>
-      <c r="Y36" s="205" t="n"/>
+      <c r="S36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y36" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z36" s="205">
         <f>SUM(O36:S36)+SUM(U36:Y36)-T36</f>
         <v/>
@@ -9929,32 +11781,104 @@
       <c r="B37" s="57" t="n">
         <v>29</v>
       </c>
-      <c r="C37" s="205" t="n"/>
-      <c r="D37" s="205" t="n"/>
+      <c r="C37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E37" s="205" t="n"/>
       <c r="F37" s="205" t="n"/>
-      <c r="G37" s="205" t="n"/>
-      <c r="H37" s="205" t="n"/>
-      <c r="I37" s="205" t="n"/>
-      <c r="J37" s="205" t="n"/>
-      <c r="K37" s="205" t="n"/>
-      <c r="L37" s="205" t="n"/>
-      <c r="M37" s="205" t="n"/>
+      <c r="G37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N37" s="205">
         <f>SUM(C37:G37)+SUM(I37:M37)-H37</f>
         <v/>
       </c>
-      <c r="O37" s="206" t="n"/>
-      <c r="P37" s="205" t="n"/>
+      <c r="O37" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q37" s="205" t="n"/>
       <c r="R37" s="205" t="n"/>
-      <c r="S37" s="205" t="n"/>
-      <c r="T37" s="205" t="n"/>
-      <c r="U37" s="205" t="n"/>
-      <c r="V37" s="205" t="n"/>
-      <c r="W37" s="205" t="n"/>
-      <c r="X37" s="205" t="n"/>
-      <c r="Y37" s="205" t="n"/>
+      <c r="S37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y37" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z37" s="205">
         <f>SUM(O37:S37)+SUM(U37:Y37)-T37</f>
         <v/>
@@ -9969,32 +11893,104 @@
       <c r="B38" s="57" t="n">
         <v>30</v>
       </c>
-      <c r="C38" s="205" t="n"/>
-      <c r="D38" s="205" t="n"/>
+      <c r="C38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E38" s="205" t="n"/>
       <c r="F38" s="205" t="n"/>
-      <c r="G38" s="205" t="n"/>
-      <c r="H38" s="205" t="n"/>
-      <c r="I38" s="205" t="n"/>
-      <c r="J38" s="205" t="n"/>
-      <c r="K38" s="205" t="n"/>
-      <c r="L38" s="205" t="n"/>
-      <c r="M38" s="205" t="n"/>
+      <c r="G38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N38" s="205">
         <f>SUM(C38:G38)+SUM(I38:M38)-H38</f>
         <v/>
       </c>
-      <c r="O38" s="206" t="n"/>
-      <c r="P38" s="205" t="n"/>
+      <c r="O38" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q38" s="205" t="n"/>
       <c r="R38" s="205" t="n"/>
-      <c r="S38" s="205" t="n"/>
-      <c r="T38" s="205" t="n"/>
-      <c r="U38" s="205" t="n"/>
-      <c r="V38" s="205" t="n"/>
-      <c r="W38" s="205" t="n"/>
-      <c r="X38" s="205" t="n"/>
-      <c r="Y38" s="205" t="n"/>
+      <c r="S38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y38" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-030:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z38" s="205">
         <f>SUM(O38:S38)+SUM(U38:Y38)-T38</f>
         <v/>
@@ -10009,32 +12005,104 @@
       <c r="B39" s="57" t="n">
         <v>31</v>
       </c>
-      <c r="C39" s="205" t="n"/>
-      <c r="D39" s="205" t="n"/>
+      <c r="C39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E39" s="205" t="n"/>
       <c r="F39" s="205" t="n"/>
-      <c r="G39" s="205" t="n"/>
-      <c r="H39" s="205" t="n"/>
-      <c r="I39" s="205" t="n"/>
-      <c r="J39" s="205" t="n"/>
-      <c r="K39" s="205" t="n"/>
-      <c r="L39" s="205" t="n"/>
-      <c r="M39" s="205" t="n"/>
+      <c r="G39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N39" s="205">
         <f>SUM(C39:G39)+SUM(I39:M39)-H39</f>
         <v/>
       </c>
-      <c r="O39" s="206" t="n"/>
-      <c r="P39" s="205" t="n"/>
+      <c r="O39" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q39" s="205" t="n"/>
       <c r="R39" s="205" t="n"/>
-      <c r="S39" s="205" t="n"/>
-      <c r="T39" s="205" t="n"/>
-      <c r="U39" s="205" t="n"/>
-      <c r="V39" s="205" t="n"/>
-      <c r="W39" s="205" t="n"/>
-      <c r="X39" s="205" t="n"/>
-      <c r="Y39" s="205" t="n"/>
+      <c r="S39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y39" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-031:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z39" s="205">
         <f>SUM(O39:S39)+SUM(U39:Y39)-T39</f>
         <v/>
@@ -10049,32 +12117,104 @@
       <c r="B40" s="57" t="n">
         <v>32</v>
       </c>
-      <c r="C40" s="205" t="n"/>
-      <c r="D40" s="205" t="n"/>
+      <c r="C40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="D40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="E40" s="205" t="n"/>
       <c r="F40" s="205" t="n"/>
-      <c r="G40" s="205" t="n"/>
-      <c r="H40" s="205" t="n"/>
-      <c r="I40" s="205" t="n"/>
-      <c r="J40" s="205" t="n"/>
-      <c r="K40" s="205" t="n"/>
-      <c r="L40" s="205" t="n"/>
-      <c r="M40" s="205" t="n"/>
+      <c r="G40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="H40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="I40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="J40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="K40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="L40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="M40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="N40" s="205">
         <f>SUM(C40:G40)+SUM(I40:M40)-H40</f>
         <v/>
       </c>
-      <c r="O40" s="206" t="n"/>
-      <c r="P40" s="205" t="n"/>
+      <c r="O40" s="206" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q40" s="205" t="n"/>
       <c r="R40" s="205" t="n"/>
-      <c r="S40" s="205" t="n"/>
-      <c r="T40" s="205" t="n"/>
-      <c r="U40" s="205" t="n"/>
-      <c r="V40" s="205" t="n"/>
-      <c r="W40" s="205" t="n"/>
-      <c r="X40" s="205" t="n"/>
-      <c r="Y40" s="205" t="n"/>
+      <c r="S40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y40" s="205" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-032:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="Z40" s="205">
         <f>SUM(O40:S40)+SUM(U40:Y40)-T40</f>
         <v/>
@@ -10234,6 +12374,9 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47" customFormat="1" s="30">
       <c r="A47" s="146" t="inlineStr">
         <is>
@@ -10358,7 +12501,7 @@
     <row r="3" ht="18" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>编制单位：</t>
+          <t>编制单位：{{company_full_name}}</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -10366,7 +12509,7 @@
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>2025年12月31日</t>
+          <t>{{audit_year}}年12月31日</t>
         </is>
       </c>
       <c r="I3" s="7" t="n"/>
@@ -10375,7 +12518,7 @@
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>金额单位：元</t>
+          <t>金额单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -10523,18 +12666,50 @@
       <c r="B7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="211" t="n"/>
-      <c r="D7" s="211" t="n"/>
-      <c r="E7" s="211" t="n"/>
-      <c r="F7" s="211" t="n"/>
+      <c r="C7" s="211" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D7" s="211" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:provision}}</t>
+        </is>
+      </c>
+      <c r="E7" s="211" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F7" s="211" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:other_increase}}</t>
+        </is>
+      </c>
       <c r="G7" s="211">
         <f>SUM(D7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="212" t="n"/>
-      <c r="I7" s="212" t="n"/>
-      <c r="J7" s="212" t="n"/>
-      <c r="K7" s="212" t="n"/>
+      <c r="H7" s="212" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:reversal}}</t>
+        </is>
+      </c>
+      <c r="I7" s="212" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:write_off}}</t>
+        </is>
+      </c>
+      <c r="J7" s="212" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K7" s="212" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-001:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L7" s="211">
         <f>SUM(H7:K7)</f>
         <v/>
@@ -10553,17 +12728,61 @@
       <c r="B8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="213" t="n"/>
-      <c r="D8" s="213" t="n"/>
-      <c r="E8" s="213" t="n"/>
-      <c r="F8" s="213" t="n"/>
-      <c r="G8" s="213" t="n"/>
-      <c r="H8" s="214" t="n"/>
-      <c r="I8" s="214" t="n"/>
-      <c r="J8" s="214" t="n"/>
-      <c r="K8" s="214" t="n"/>
-      <c r="L8" s="213" t="n"/>
-      <c r="M8" s="213" t="n"/>
+      <c r="C8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:provision}}</t>
+        </is>
+      </c>
+      <c r="E8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:other_increase}}</t>
+        </is>
+      </c>
+      <c r="G8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:subtotal_increase}}</t>
+        </is>
+      </c>
+      <c r="H8" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:reversal}}</t>
+        </is>
+      </c>
+      <c r="I8" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:write_off}}</t>
+        </is>
+      </c>
+      <c r="J8" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K8" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:other_decrease}}</t>
+        </is>
+      </c>
+      <c r="L8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:subtotal_decrease}}</t>
+        </is>
+      </c>
+      <c r="M8" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-002:closing_balance}}</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customFormat="1" customHeight="1" s="2">
       <c r="A9" s="18" t="inlineStr">
@@ -10574,18 +12793,50 @@
       <c r="B9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="213" t="n"/>
-      <c r="D9" s="213" t="n"/>
-      <c r="E9" s="213" t="n"/>
-      <c r="F9" s="213" t="n"/>
+      <c r="C9" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D9" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:provision}}</t>
+        </is>
+      </c>
+      <c r="E9" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F9" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:other_increase}}</t>
+        </is>
+      </c>
       <c r="G9" s="213">
         <f>SUM(D9:F9)</f>
         <v/>
       </c>
-      <c r="H9" s="214" t="n"/>
-      <c r="I9" s="214" t="n"/>
-      <c r="J9" s="214" t="n"/>
-      <c r="K9" s="214" t="n"/>
+      <c r="H9" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:reversal}}</t>
+        </is>
+      </c>
+      <c r="I9" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:write_off}}</t>
+        </is>
+      </c>
+      <c r="J9" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K9" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-003:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L9" s="213">
         <f>SUM(H9:K9)</f>
         <v/>
@@ -10604,18 +12855,50 @@
       <c r="B10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="213" t="n"/>
-      <c r="D10" s="213" t="n"/>
-      <c r="E10" s="213" t="n"/>
-      <c r="F10" s="213" t="n"/>
+      <c r="C10" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D10" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:provision}}</t>
+        </is>
+      </c>
+      <c r="E10" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F10" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:other_increase}}</t>
+        </is>
+      </c>
       <c r="G10" s="213">
         <f>SUM(D10:F10)</f>
         <v/>
       </c>
-      <c r="H10" s="214" t="n"/>
-      <c r="I10" s="214" t="n"/>
-      <c r="J10" s="214" t="n"/>
-      <c r="K10" s="214" t="n"/>
+      <c r="H10" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:reversal}}</t>
+        </is>
+      </c>
+      <c r="I10" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:write_off}}</t>
+        </is>
+      </c>
+      <c r="J10" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K10" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-004:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L10" s="213">
         <f>SUM(H10:K10)</f>
         <v/>
@@ -10634,18 +12917,50 @@
       <c r="B11" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="213" t="n"/>
-      <c r="D11" s="213" t="n"/>
-      <c r="E11" s="213" t="n"/>
-      <c r="F11" s="213" t="n"/>
+      <c r="C11" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D11" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:provision}}</t>
+        </is>
+      </c>
+      <c r="E11" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F11" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:other_increase}}</t>
+        </is>
+      </c>
       <c r="G11" s="213">
         <f>SUM(D11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="215" t="n"/>
-      <c r="I11" s="214" t="n"/>
-      <c r="J11" s="214" t="n"/>
-      <c r="K11" s="214" t="n"/>
+      <c r="H11" s="215" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:reversal}}</t>
+        </is>
+      </c>
+      <c r="I11" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:write_off}}</t>
+        </is>
+      </c>
+      <c r="J11" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K11" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-005:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L11" s="213">
         <f>SUM(H11:K11)</f>
         <v/>
@@ -10664,18 +12979,50 @@
       <c r="B12" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="213" t="n"/>
-      <c r="D12" s="213" t="n"/>
-      <c r="E12" s="213" t="n"/>
-      <c r="F12" s="213" t="n"/>
+      <c r="C12" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D12" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:provision}}</t>
+        </is>
+      </c>
+      <c r="E12" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F12" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:other_increase}}</t>
+        </is>
+      </c>
       <c r="G12" s="213">
         <f>SUM(D12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="214" t="n"/>
-      <c r="I12" s="214" t="n"/>
-      <c r="J12" s="214" t="n"/>
-      <c r="K12" s="214" t="n"/>
+      <c r="H12" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:reversal}}</t>
+        </is>
+      </c>
+      <c r="I12" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:write_off}}</t>
+        </is>
+      </c>
+      <c r="J12" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K12" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-006:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L12" s="213">
         <f>SUM(H12:K12)</f>
         <v/>
@@ -10694,22 +13041,50 @@
       <c r="B13" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="213" t="n"/>
-      <c r="D13" s="213" t="n"/>
-      <c r="E13" s="213" t="n"/>
-      <c r="F13" s="213" t="n"/>
+      <c r="C13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:provision}}</t>
+        </is>
+      </c>
+      <c r="E13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:other_increase}}</t>
+        </is>
+      </c>
       <c r="G13" s="213">
         <f>SUM(D13:F13)</f>
         <v/>
       </c>
       <c r="H13" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I13" s="214" t="n"/>
-      <c r="J13" s="213" t="n"/>
-      <c r="K13" s="213" t="n"/>
+          <t>{{imp:IMP-007:reversal}}</t>
+        </is>
+      </c>
+      <c r="I13" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:write_off}}</t>
+        </is>
+      </c>
+      <c r="J13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K13" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-007:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L13" s="213">
         <f>SUM(H13:K13)</f>
         <v/>
@@ -10728,18 +13103,50 @@
       <c r="B14" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="213" t="n"/>
-      <c r="D14" s="213" t="n"/>
-      <c r="E14" s="213" t="n"/>
-      <c r="F14" s="213" t="n"/>
+      <c r="C14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:provision}}</t>
+        </is>
+      </c>
+      <c r="E14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:other_increase}}</t>
+        </is>
+      </c>
       <c r="G14" s="213">
         <f>SUM(D14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="215" t="n"/>
-      <c r="I14" s="213" t="n"/>
-      <c r="J14" s="213" t="n"/>
-      <c r="K14" s="213" t="n"/>
+      <c r="H14" s="215" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:reversal}}</t>
+        </is>
+      </c>
+      <c r="I14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:write_off}}</t>
+        </is>
+      </c>
+      <c r="J14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K14" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-008:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L14" s="213">
         <f>SUM(I14:K14)</f>
         <v/>
@@ -10758,22 +13165,50 @@
       <c r="B15" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="213" t="n"/>
-      <c r="D15" s="213" t="n"/>
-      <c r="E15" s="213" t="n"/>
-      <c r="F15" s="213" t="n"/>
+      <c r="C15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:provision}}</t>
+        </is>
+      </c>
+      <c r="E15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:other_increase}}</t>
+        </is>
+      </c>
       <c r="G15" s="213">
         <f>SUM(D15:F15)</f>
         <v/>
       </c>
       <c r="H15" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I15" s="213" t="n"/>
-      <c r="J15" s="213" t="n"/>
-      <c r="K15" s="213" t="n"/>
+          <t>{{imp:IMP-009:reversal}}</t>
+        </is>
+      </c>
+      <c r="I15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:write_off}}</t>
+        </is>
+      </c>
+      <c r="J15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K15" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-009:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L15" s="213">
         <f>SUM(I15:K15)</f>
         <v/>
@@ -10792,22 +13227,50 @@
       <c r="B16" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="213" t="n"/>
-      <c r="D16" s="213" t="n"/>
-      <c r="E16" s="213" t="n"/>
-      <c r="F16" s="213" t="n"/>
+      <c r="C16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:provision}}</t>
+        </is>
+      </c>
+      <c r="E16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:other_increase}}</t>
+        </is>
+      </c>
       <c r="G16" s="213">
         <f>SUM(D16:F16)</f>
         <v/>
       </c>
       <c r="H16" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I16" s="213" t="n"/>
-      <c r="J16" s="213" t="n"/>
-      <c r="K16" s="213" t="n"/>
+          <t>{{imp:IMP-010:reversal}}</t>
+        </is>
+      </c>
+      <c r="I16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:write_off}}</t>
+        </is>
+      </c>
+      <c r="J16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K16" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-010:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L16" s="213">
         <f>SUM(I16:K16)</f>
         <v/>
@@ -10826,22 +13289,50 @@
       <c r="B17" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="213" t="n"/>
-      <c r="D17" s="213" t="n"/>
-      <c r="E17" s="213" t="n"/>
-      <c r="F17" s="213" t="n"/>
+      <c r="C17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:provision}}</t>
+        </is>
+      </c>
+      <c r="E17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:other_increase}}</t>
+        </is>
+      </c>
       <c r="G17" s="213">
         <f>SUM(D17:F17)</f>
         <v/>
       </c>
       <c r="H17" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I17" s="214" t="n"/>
-      <c r="J17" s="213" t="n"/>
-      <c r="K17" s="213" t="n"/>
+          <t>{{imp:IMP-011:reversal}}</t>
+        </is>
+      </c>
+      <c r="I17" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:write_off}}</t>
+        </is>
+      </c>
+      <c r="J17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K17" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-011:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L17" s="213">
         <f>SUM(I17:K17)</f>
         <v/>
@@ -10860,22 +13351,50 @@
       <c r="B18" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="213" t="n"/>
-      <c r="D18" s="213" t="n"/>
-      <c r="E18" s="213" t="n"/>
-      <c r="F18" s="213" t="n"/>
+      <c r="C18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:provision}}</t>
+        </is>
+      </c>
+      <c r="E18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:other_increase}}</t>
+        </is>
+      </c>
       <c r="G18" s="213">
         <f>SUM(D18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I18" s="213" t="n"/>
-      <c r="J18" s="213" t="n"/>
-      <c r="K18" s="213" t="n"/>
+          <t>{{imp:IMP-012:reversal}}</t>
+        </is>
+      </c>
+      <c r="I18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:write_off}}</t>
+        </is>
+      </c>
+      <c r="J18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K18" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-012:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L18" s="213">
         <f>SUM(I18:K18)</f>
         <v/>
@@ -10894,24 +13413,60 @@
       <c r="B19" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="213" t="n"/>
-      <c r="D19" s="213" t="n"/>
-      <c r="E19" s="213" t="n"/>
-      <c r="F19" s="213" t="n"/>
+      <c r="C19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:provision}}</t>
+        </is>
+      </c>
+      <c r="E19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:other_increase}}</t>
+        </is>
+      </c>
       <c r="G19" s="213">
         <f>SUM(D19:F19)</f>
         <v/>
       </c>
       <c r="H19" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I19" s="213" t="n"/>
-      <c r="J19" s="213" t="n"/>
-      <c r="K19" s="213" t="n"/>
-      <c r="L19" s="213" t="n"/>
-      <c r="M19" s="213" t="n"/>
+          <t>{{imp:IMP-013:reversal}}</t>
+        </is>
+      </c>
+      <c r="I19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:write_off}}</t>
+        </is>
+      </c>
+      <c r="J19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:other_decrease}}</t>
+        </is>
+      </c>
+      <c r="L19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:subtotal_decrease}}</t>
+        </is>
+      </c>
+      <c r="M19" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-013:closing_balance}}</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22.2" customFormat="1" customHeight="1" s="2">
       <c r="A20" s="18" t="inlineStr">
@@ -10922,22 +13477,50 @@
       <c r="B20" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="213" t="n"/>
-      <c r="D20" s="213" t="n"/>
-      <c r="E20" s="213" t="n"/>
-      <c r="F20" s="213" t="n"/>
+      <c r="C20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:provision}}</t>
+        </is>
+      </c>
+      <c r="E20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:other_increase}}</t>
+        </is>
+      </c>
       <c r="G20" s="213">
         <f>SUM(D20:F20)</f>
         <v/>
       </c>
       <c r="H20" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I20" s="214" t="n"/>
-      <c r="J20" s="213" t="n"/>
-      <c r="K20" s="213" t="n"/>
+          <t>{{imp:IMP-014:reversal}}</t>
+        </is>
+      </c>
+      <c r="I20" s="214" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:write_off}}</t>
+        </is>
+      </c>
+      <c r="J20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K20" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-014:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L20" s="213">
         <f>SUM(I20:K20)</f>
         <v/>
@@ -10956,22 +13539,50 @@
       <c r="B21" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="213" t="n"/>
-      <c r="D21" s="213" t="n"/>
-      <c r="E21" s="213" t="n"/>
-      <c r="F21" s="213" t="n"/>
+      <c r="C21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:provision}}</t>
+        </is>
+      </c>
+      <c r="E21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:other_increase}}</t>
+        </is>
+      </c>
       <c r="G21" s="213">
         <f>SUM(D21:F21)</f>
         <v/>
       </c>
       <c r="H21" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I21" s="213" t="n"/>
-      <c r="J21" s="213" t="n"/>
-      <c r="K21" s="213" t="n"/>
+          <t>{{imp:IMP-015:reversal}}</t>
+        </is>
+      </c>
+      <c r="I21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:write_off}}</t>
+        </is>
+      </c>
+      <c r="J21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K21" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-015:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L21" s="213">
         <f>SUM(H21:K21)</f>
         <v/>
@@ -10990,22 +13601,50 @@
       <c r="B22" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="213" t="n"/>
-      <c r="D22" s="213" t="n"/>
-      <c r="E22" s="213" t="n"/>
-      <c r="F22" s="213" t="n"/>
+      <c r="C22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:provision}}</t>
+        </is>
+      </c>
+      <c r="E22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:other_increase}}</t>
+        </is>
+      </c>
       <c r="G22" s="213">
         <f>SUM(D22:F22)</f>
         <v/>
       </c>
       <c r="H22" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I22" s="213" t="n"/>
-      <c r="J22" s="213" t="n"/>
-      <c r="K22" s="213" t="n"/>
+          <t>{{imp:IMP-016:reversal}}</t>
+        </is>
+      </c>
+      <c r="I22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:write_off}}</t>
+        </is>
+      </c>
+      <c r="J22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K22" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-016:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L22" s="213">
         <f>SUM(I22:K22)</f>
         <v/>
@@ -11024,22 +13663,50 @@
       <c r="B23" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="213" t="n"/>
-      <c r="D23" s="213" t="n"/>
-      <c r="E23" s="213" t="n"/>
-      <c r="F23" s="213" t="n"/>
+      <c r="C23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:provision}}</t>
+        </is>
+      </c>
+      <c r="E23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:other_increase}}</t>
+        </is>
+      </c>
       <c r="G23" s="213">
         <f>SUM(D23:F23)</f>
         <v/>
       </c>
       <c r="H23" s="215" t="inlineStr">
         <is>
-          <t>——</t>
-        </is>
-      </c>
-      <c r="I23" s="213" t="n"/>
-      <c r="J23" s="213" t="n"/>
-      <c r="K23" s="213" t="n"/>
+          <t>{{imp:IMP-017:reversal}}</t>
+        </is>
+      </c>
+      <c r="I23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:write_off}}</t>
+        </is>
+      </c>
+      <c r="J23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K23" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-017:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L23" s="213">
         <f>SUM(H23:K23)</f>
         <v/>
@@ -11058,18 +13725,50 @@
       <c r="B24" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="213" t="n"/>
-      <c r="D24" s="213" t="n"/>
-      <c r="E24" s="213" t="n"/>
-      <c r="F24" s="213" t="n"/>
+      <c r="C24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:opening_balance}}</t>
+        </is>
+      </c>
+      <c r="D24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:provision}}</t>
+        </is>
+      </c>
+      <c r="E24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:merge_increase}}</t>
+        </is>
+      </c>
+      <c r="F24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:other_increase}}</t>
+        </is>
+      </c>
       <c r="G24" s="213">
         <f>SUM(D24:F24)</f>
         <v/>
       </c>
-      <c r="H24" s="216" t="n"/>
-      <c r="I24" s="213" t="n"/>
-      <c r="J24" s="213" t="n"/>
-      <c r="K24" s="213" t="n"/>
+      <c r="H24" s="216" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:reversal}}</t>
+        </is>
+      </c>
+      <c r="I24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:write_off}}</t>
+        </is>
+      </c>
+      <c r="J24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:merge_decrease}}</t>
+        </is>
+      </c>
+      <c r="K24" s="213" t="inlineStr">
+        <is>
+          <t>{{imp:IMP-018:other_decrease}}</t>
+        </is>
+      </c>
       <c r="L24" s="213">
         <f>SUM(I24:K24)</f>
         <v/>
